--- a/research/traditional_assets/database/data/czech_republic/czech_republic_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00716</v>
+        <v>0.0395</v>
       </c>
       <c r="E2">
-        <v>-0.0389</v>
+        <v>0.0459</v>
       </c>
       <c r="F2">
-        <v>0.224</v>
+        <v>0.0755</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>650.8</v>
+        <v>888.9</v>
       </c>
       <c r="L2">
-        <v>0.373186535925225</v>
+        <v>0.4597600082755767</v>
       </c>
       <c r="M2">
-        <v>275.908</v>
+        <v>203.6</v>
       </c>
       <c r="N2">
-        <v>0.02702066398981491</v>
+        <v>0.02831474424943676</v>
       </c>
       <c r="O2">
-        <v>0.4239520590043024</v>
+        <v>0.2290471369107886</v>
       </c>
       <c r="P2">
-        <v>275.908</v>
+        <v>203.6</v>
       </c>
       <c r="Q2">
-        <v>0.02702066398981491</v>
+        <v>0.02831474424943676</v>
       </c>
       <c r="R2">
-        <v>0.4239520590043024</v>
+        <v>0.2290471369107886</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4095.4</v>
+        <v>1556.4</v>
       </c>
       <c r="V2">
-        <v>0.4010772696112036</v>
+        <v>0.2164492531916669</v>
       </c>
       <c r="W2">
-        <v>0.1218425091537354</v>
+        <v>0.1358654734073531</v>
       </c>
       <c r="X2">
-        <v>0.05460642032369926</v>
+        <v>0.09598211896909824</v>
       </c>
       <c r="Y2">
-        <v>0.06723608883003611</v>
+        <v>0.03988335443825482</v>
       </c>
       <c r="Z2">
-        <v>0.1353812473799432</v>
+        <v>0.2159547850951657</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04376135580946207</v>
+        <v>0.07092928345853342</v>
       </c>
       <c r="AC2">
-        <v>-0.04376135580946207</v>
+        <v>-0.07092928345853342</v>
       </c>
       <c r="AD2">
-        <v>6010.900000000001</v>
+        <v>10566.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6010.900000000001</v>
+        <v>10566.1</v>
       </c>
       <c r="AG2">
-        <v>1915.5</v>
+        <v>9009.700000000001</v>
       </c>
       <c r="AH2">
-        <v>0.3705422915934631</v>
+        <v>0.5950486295313882</v>
       </c>
       <c r="AI2">
-        <v>0.4552367103658768</v>
+        <v>0.6247065987926946</v>
       </c>
       <c r="AJ2">
-        <v>0.1579598400197914</v>
+        <v>0.5561440220242835</v>
       </c>
       <c r="AK2">
-        <v>0.2102980732283033</v>
+        <v>0.5866721363781394</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00752</v>
+        <v>0.0424</v>
       </c>
       <c r="E3">
-        <v>-0.0309</v>
+        <v>0.055</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,28 +731,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>164</v>
+        <v>207.6</v>
       </c>
       <c r="L3">
-        <v>0.3598858898398069</v>
+        <v>0.4342187826814474</v>
       </c>
       <c r="M3">
-        <v>70.00700000000001</v>
+        <v>203.6</v>
       </c>
       <c r="N3">
-        <v>0.03212656601349181</v>
+        <v>0.1185029974972353</v>
       </c>
       <c r="O3">
-        <v>0.4268719512195122</v>
+        <v>0.9807321772639692</v>
       </c>
       <c r="P3">
-        <v>70.00700000000001</v>
+        <v>203.6</v>
       </c>
       <c r="Q3">
-        <v>0.03212656601349181</v>
+        <v>0.1185029974972353</v>
       </c>
       <c r="R3">
-        <v>0.4268719512195122</v>
+        <v>0.9807321772639692</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>475.1</v>
+        <v>540.4</v>
       </c>
       <c r="V3">
-        <v>0.218025790463953</v>
+        <v>0.3145334963040568</v>
       </c>
       <c r="W3">
-        <v>0.1431314365508815</v>
+        <v>0.1515107283608232</v>
       </c>
       <c r="X3">
-        <v>0.05352160420274957</v>
+        <v>0.07628493480237664</v>
       </c>
       <c r="Y3">
-        <v>0.08960983234813191</v>
+        <v>0.07522579355844658</v>
       </c>
       <c r="Z3">
-        <v>0.2116090085906664</v>
+        <v>0.2379909403155956</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04322365951284934</v>
+        <v>0.06951899054297421</v>
       </c>
       <c r="AC3">
-        <v>-0.04322365951284934</v>
+        <v>-0.06951899054297421</v>
       </c>
       <c r="AD3">
-        <v>1113.8</v>
+        <v>460.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1113.8</v>
+        <v>460.1</v>
       </c>
       <c r="AG3">
-        <v>638.6999999999999</v>
+        <v>-80.29999999999995</v>
       </c>
       <c r="AH3">
-        <v>0.338242886209724</v>
+        <v>0.211229455513727</v>
       </c>
       <c r="AI3">
-        <v>0.448389694041868</v>
+        <v>0.2777375347096463</v>
       </c>
       <c r="AJ3">
-        <v>0.2266661934842785</v>
+        <v>-0.04902918549273413</v>
       </c>
       <c r="AK3">
-        <v>0.3179351884115685</v>
+        <v>-0.07194051245296537</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0068</v>
+        <v>0.0366</v>
       </c>
       <c r="E4">
-        <v>-0.0469</v>
+        <v>0.0368</v>
       </c>
       <c r="F4">
-        <v>0.224</v>
+        <v>0.0755</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,85 +856,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>486.8</v>
+        <v>681.3</v>
       </c>
       <c r="L4">
-        <v>0.3778916317342028</v>
+        <v>0.4681508967223253</v>
       </c>
       <c r="M4">
-        <v>205.901</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.02563540382723889</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.422968364831553</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>205.901</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.02563540382723889</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.422968364831553</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>3620.3</v>
+        <v>1016</v>
       </c>
       <c r="V4">
-        <v>0.4507401735579378</v>
+        <v>0.1856555504796711</v>
       </c>
       <c r="W4">
-        <v>0.1005535817565893</v>
+        <v>0.1202202184538829</v>
       </c>
       <c r="X4">
-        <v>0.05569123644464895</v>
+        <v>0.1156793031358198</v>
       </c>
       <c r="Y4">
-        <v>0.04486234531194033</v>
+        <v>0.004540915318063082</v>
       </c>
       <c r="Z4">
-        <v>0.1200794190848162</v>
+        <v>0.2095796310430738</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04429905210607479</v>
+        <v>0.07233957637409261</v>
       </c>
       <c r="AC4">
-        <v>-0.04429905210607479</v>
+        <v>-0.07233957637409261</v>
       </c>
       <c r="AD4">
-        <v>4897.1</v>
+        <v>10106</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4897.1</v>
+        <v>10106</v>
       </c>
       <c r="AG4">
-        <v>1276.8</v>
+        <v>9090</v>
       </c>
       <c r="AH4">
-        <v>0.3787686596024442</v>
+        <v>0.648714574573932</v>
       </c>
       <c r="AI4">
-        <v>0.4568232912620454</v>
+        <v>0.6623801377719226</v>
       </c>
       <c r="AJ4">
-        <v>0.1371620097328306</v>
+        <v>0.624206008583691</v>
       </c>
       <c r="AK4">
-        <v>0.1798411178094541</v>
+        <v>0.638293390257775</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/czech_republic/czech_republic_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0395</v>
+        <v>0.02995</v>
       </c>
       <c r="E2">
-        <v>0.0459</v>
+        <v>0.0338</v>
       </c>
       <c r="F2">
-        <v>0.0755</v>
+        <v>-0.0101</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>888.9</v>
+        <v>952.5</v>
       </c>
       <c r="L2">
-        <v>0.4597600082755767</v>
+        <v>0.4432500349015775</v>
       </c>
       <c r="M2">
-        <v>203.6</v>
+        <v>672.3180000000001</v>
       </c>
       <c r="N2">
-        <v>0.02831474424943676</v>
+        <v>0.08136684901002084</v>
       </c>
       <c r="O2">
-        <v>0.2290471369107886</v>
+        <v>0.7058456692913387</v>
       </c>
       <c r="P2">
-        <v>203.6</v>
+        <v>672.3180000000001</v>
       </c>
       <c r="Q2">
-        <v>0.02831474424943676</v>
+        <v>0.08136684901002084</v>
       </c>
       <c r="R2">
-        <v>0.2290471369107886</v>
+        <v>0.7058456692913387</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1556.4</v>
+        <v>1179.7</v>
       </c>
       <c r="V2">
-        <v>0.2164492531916669</v>
+        <v>0.1427724258120734</v>
       </c>
       <c r="W2">
-        <v>0.1358654734073531</v>
+        <v>0.1643631611655502</v>
       </c>
       <c r="X2">
-        <v>0.09598211896909824</v>
+        <v>0.07507935768821503</v>
       </c>
       <c r="Y2">
-        <v>0.03988335443825482</v>
+        <v>0.08928380347733514</v>
       </c>
       <c r="Z2">
-        <v>0.2159547850951657</v>
+        <v>0.1425151209677419</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07092928345853342</v>
+        <v>0.06092615816824991</v>
       </c>
       <c r="AC2">
-        <v>-0.07092928345853342</v>
+        <v>-0.06092615816824991</v>
       </c>
       <c r="AD2">
-        <v>10566.1</v>
+        <v>8907.799999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10566.1</v>
+        <v>8907.799999999999</v>
       </c>
       <c r="AG2">
-        <v>9009.700000000001</v>
+        <v>7728.099999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5950486295313882</v>
+        <v>0.51878210429455</v>
       </c>
       <c r="AI2">
-        <v>0.6247065987926946</v>
+        <v>0.5681176057910009</v>
       </c>
       <c r="AJ2">
-        <v>0.5561440220242835</v>
+        <v>0.4832811161348017</v>
       </c>
       <c r="AK2">
-        <v>0.5866721363781394</v>
+        <v>0.5329797652381412</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0424</v>
+        <v>0.0288</v>
       </c>
       <c r="E3">
-        <v>0.055</v>
+        <v>0.0386</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,28 +731,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>207.6</v>
+        <v>218.5</v>
       </c>
       <c r="L3">
-        <v>0.4342187826814474</v>
+        <v>0.4316475701303832</v>
       </c>
       <c r="M3">
-        <v>203.6</v>
+        <v>177.4</v>
       </c>
       <c r="N3">
-        <v>0.1185029974972353</v>
+        <v>0.08288944958415102</v>
       </c>
       <c r="O3">
-        <v>0.9807321772639692</v>
+        <v>0.8118993135011442</v>
       </c>
       <c r="P3">
-        <v>203.6</v>
+        <v>177.4</v>
       </c>
       <c r="Q3">
-        <v>0.1185029974972353</v>
+        <v>0.08288944958415102</v>
       </c>
       <c r="R3">
-        <v>0.9807321772639692</v>
+        <v>0.8118993135011442</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>540.4</v>
+        <v>676.9</v>
       </c>
       <c r="V3">
-        <v>0.3145334963040568</v>
+        <v>0.3162788524436969</v>
       </c>
       <c r="W3">
-        <v>0.1515107283608232</v>
+        <v>0.1826159632260761</v>
       </c>
       <c r="X3">
-        <v>0.07628493480237664</v>
+        <v>0.0665640353706107</v>
       </c>
       <c r="Y3">
-        <v>0.07522579355844658</v>
+        <v>0.1160519278554654</v>
       </c>
       <c r="Z3">
-        <v>0.2379909403155956</v>
+        <v>0.453502956459416</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06951899054297421</v>
+        <v>0.06006409378538693</v>
       </c>
       <c r="AC3">
-        <v>-0.06951899054297421</v>
+        <v>-0.06006409378538693</v>
       </c>
       <c r="AD3">
-        <v>460.1</v>
+        <v>760.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>460.1</v>
+        <v>760.6</v>
       </c>
       <c r="AG3">
-        <v>-80.29999999999995</v>
+        <v>83.70000000000005</v>
       </c>
       <c r="AH3">
-        <v>0.211229455513727</v>
+        <v>0.2622035300606729</v>
       </c>
       <c r="AI3">
-        <v>0.2777375347096463</v>
+        <v>0.361416013304823</v>
       </c>
       <c r="AJ3">
-        <v>-0.04902918549273413</v>
+        <v>0.03763658437879404</v>
       </c>
       <c r="AK3">
-        <v>-0.07194051245296537</v>
+        <v>0.05862986831045113</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0366</v>
+        <v>0.0311</v>
       </c>
       <c r="E4">
-        <v>0.0368</v>
+        <v>0.029</v>
       </c>
       <c r="F4">
-        <v>0.0755</v>
+        <v>-0.0101</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,82 +856,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>681.3</v>
+        <v>734</v>
       </c>
       <c r="L4">
-        <v>0.4681508967223253</v>
+        <v>0.4468253485115968</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>494.9180000000001</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.08083461274621893</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.6742752043596731</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>494.9180000000001</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.08083461274621893</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.6742752043596731</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>1016</v>
+        <v>502.8</v>
       </c>
       <c r="V4">
-        <v>0.1856555504796711</v>
+        <v>0.08212197432463332</v>
       </c>
       <c r="W4">
-        <v>0.1202202184538829</v>
+        <v>0.1461103591050243</v>
       </c>
       <c r="X4">
-        <v>0.1156793031358198</v>
+        <v>0.08359468000581935</v>
       </c>
       <c r="Y4">
-        <v>0.004540915318063082</v>
+        <v>0.06251567909920491</v>
       </c>
       <c r="Z4">
-        <v>0.2095796310430738</v>
+        <v>0.1176533784074143</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07233957637409261</v>
+        <v>0.06178822255111288</v>
       </c>
       <c r="AC4">
-        <v>-0.07233957637409261</v>
+        <v>-0.06178822255111288</v>
       </c>
       <c r="AD4">
-        <v>10106</v>
+        <v>8147.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>10106</v>
+        <v>8147.2</v>
       </c>
       <c r="AG4">
-        <v>9090</v>
+        <v>7644.4</v>
       </c>
       <c r="AH4">
-        <v>0.648714574573932</v>
+        <v>0.57094002719029</v>
       </c>
       <c r="AI4">
-        <v>0.6623801377719226</v>
+        <v>0.6001620626151013</v>
       </c>
       <c r="AJ4">
-        <v>0.624206008583691</v>
+        <v>0.5552698481876952</v>
       </c>
       <c r="AK4">
-        <v>0.638293390257775</v>
+        <v>0.5847829745566928</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/czech_republic/czech_republic_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.02995</v>
+        <v>0.00409</v>
       </c>
       <c r="E2">
-        <v>0.0338</v>
+        <v>0.0111</v>
       </c>
       <c r="F2">
-        <v>-0.0101</v>
+        <v>0.0421</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>952.5</v>
+        <v>698.4</v>
       </c>
       <c r="L2">
-        <v>0.4432500349015775</v>
+        <v>0.4657552517505835</v>
       </c>
       <c r="M2">
-        <v>672.3180000000001</v>
+        <v>689.485</v>
       </c>
       <c r="N2">
-        <v>0.08136684901002084</v>
+        <v>0.1047212940461725</v>
       </c>
       <c r="O2">
-        <v>0.7058456692913387</v>
+        <v>0.9872351088201604</v>
       </c>
       <c r="P2">
-        <v>672.3180000000001</v>
+        <v>689.485</v>
       </c>
       <c r="Q2">
-        <v>0.08136684901002084</v>
+        <v>0.1047212940461725</v>
       </c>
       <c r="R2">
-        <v>0.7058456692913387</v>
+        <v>0.9872351088201604</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1179.7</v>
+        <v>1074.9</v>
       </c>
       <c r="V2">
-        <v>0.1427724258120734</v>
+        <v>0.1632594167679222</v>
       </c>
       <c r="W2">
-        <v>0.1643631611655502</v>
+        <v>0.1320476460578559</v>
       </c>
       <c r="X2">
-        <v>0.07507935768821503</v>
+        <v>0.08271184774683492</v>
       </c>
       <c r="Y2">
-        <v>0.08928380347733514</v>
+        <v>0.04933579831102101</v>
       </c>
       <c r="Z2">
-        <v>0.1425151209677419</v>
+        <v>0.1174374437091279</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06092615816824991</v>
+        <v>0.06557648678154986</v>
       </c>
       <c r="AC2">
-        <v>-0.06092615816824991</v>
+        <v>-0.06557648678154986</v>
       </c>
       <c r="AD2">
-        <v>8907.799999999999</v>
+        <v>6721.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8907.799999999999</v>
+        <v>6721.5</v>
       </c>
       <c r="AG2">
-        <v>7728.099999999999</v>
+        <v>5646.6</v>
       </c>
       <c r="AH2">
-        <v>0.51878210429455</v>
+        <v>0.5051670361880425</v>
       </c>
       <c r="AI2">
-        <v>0.5681176057910009</v>
+        <v>0.548568490467485</v>
       </c>
       <c r="AJ2">
-        <v>0.4832811161348017</v>
+        <v>0.4616780861118833</v>
       </c>
       <c r="AK2">
-        <v>0.5329797652381412</v>
+        <v>0.5051574982778518</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MONETA Money Bank, a.s. (SEP:MONET)</t>
+          <t>Komercní banka, a.s. (SEP:KOMB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0288</v>
+        <v>0.00409</v>
       </c>
       <c r="E3">
-        <v>0.0386</v>
+        <v>0.0111</v>
+      </c>
+      <c r="F3">
+        <v>0.0421</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>218.5</v>
+        <v>698.4</v>
       </c>
       <c r="L3">
-        <v>0.4316475701303832</v>
+        <v>0.4657552517505835</v>
       </c>
       <c r="M3">
-        <v>177.4</v>
+        <v>689.485</v>
       </c>
       <c r="N3">
-        <v>0.08288944958415102</v>
+        <v>0.1047212940461725</v>
       </c>
       <c r="O3">
-        <v>0.8118993135011442</v>
+        <v>0.9872351088201604</v>
       </c>
       <c r="P3">
-        <v>177.4</v>
+        <v>689.485</v>
       </c>
       <c r="Q3">
-        <v>0.08288944958415102</v>
+        <v>0.1047212940461725</v>
       </c>
       <c r="R3">
-        <v>0.8118993135011442</v>
+        <v>0.9872351088201604</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,185 +764,60 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>676.9</v>
+        <v>1074.9</v>
       </c>
       <c r="V3">
-        <v>0.3162788524436969</v>
+        <v>0.1632594167679222</v>
       </c>
       <c r="W3">
-        <v>0.1826159632260761</v>
+        <v>0.1320476460578559</v>
       </c>
       <c r="X3">
-        <v>0.0665640353706107</v>
+        <v>0.08271184774683492</v>
       </c>
       <c r="Y3">
-        <v>0.1160519278554654</v>
+        <v>0.04933579831102101</v>
       </c>
       <c r="Z3">
-        <v>0.453502956459416</v>
+        <v>0.1174374437091279</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06006409378538693</v>
+        <v>0.06557648678154986</v>
       </c>
       <c r="AC3">
-        <v>-0.06006409378538693</v>
+        <v>-0.06557648678154986</v>
       </c>
       <c r="AD3">
-        <v>760.6</v>
+        <v>6721.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>760.6</v>
+        <v>6721.5</v>
       </c>
       <c r="AG3">
-        <v>83.70000000000005</v>
+        <v>5646.6</v>
       </c>
       <c r="AH3">
-        <v>0.2622035300606729</v>
+        <v>0.5051670361880425</v>
       </c>
       <c r="AI3">
-        <v>0.361416013304823</v>
+        <v>0.548568490467485</v>
       </c>
       <c r="AJ3">
-        <v>0.03763658437879404</v>
+        <v>0.4616780861118833</v>
       </c>
       <c r="AK3">
-        <v>0.05862986831045113</v>
+        <v>0.5051574982778518</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Czech Republic</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Komercní banka, a.s. (SEP:KOMB)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0311</v>
-      </c>
-      <c r="E4">
-        <v>0.029</v>
-      </c>
-      <c r="F4">
-        <v>-0.0101</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>734</v>
-      </c>
-      <c r="L4">
-        <v>0.4468253485115968</v>
-      </c>
-      <c r="M4">
-        <v>494.9180000000001</v>
-      </c>
-      <c r="N4">
-        <v>0.08083461274621893</v>
-      </c>
-      <c r="O4">
-        <v>0.6742752043596731</v>
-      </c>
-      <c r="P4">
-        <v>494.9180000000001</v>
-      </c>
-      <c r="Q4">
-        <v>0.08083461274621893</v>
-      </c>
-      <c r="R4">
-        <v>0.6742752043596731</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>502.8</v>
-      </c>
-      <c r="V4">
-        <v>0.08212197432463332</v>
-      </c>
-      <c r="W4">
-        <v>0.1461103591050243</v>
-      </c>
-      <c r="X4">
-        <v>0.08359468000581935</v>
-      </c>
-      <c r="Y4">
-        <v>0.06251567909920491</v>
-      </c>
-      <c r="Z4">
-        <v>0.1176533784074143</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.06178822255111288</v>
-      </c>
-      <c r="AC4">
-        <v>-0.06178822255111288</v>
-      </c>
-      <c r="AD4">
-        <v>8147.2</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>8147.2</v>
-      </c>
-      <c r="AG4">
-        <v>7644.4</v>
-      </c>
-      <c r="AH4">
-        <v>0.57094002719029</v>
-      </c>
-      <c r="AI4">
-        <v>0.6001620626151013</v>
-      </c>
-      <c r="AJ4">
-        <v>0.5552698481876952</v>
-      </c>
-      <c r="AK4">
-        <v>0.5847829745566928</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/czech_republic/czech_republic_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00409</v>
+        <v>0.022395</v>
       </c>
       <c r="E2">
-        <v>0.0111</v>
+        <v>0.04025</v>
       </c>
       <c r="F2">
         <v>0.0421</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>698.4</v>
+        <v>940</v>
       </c>
       <c r="L2">
-        <v>0.4657552517505835</v>
+        <v>0.4622571920334399</v>
       </c>
       <c r="M2">
-        <v>689.485</v>
+        <v>892.7850000000001</v>
       </c>
       <c r="N2">
-        <v>0.1047212940461725</v>
+        <v>0.09721937886575485</v>
       </c>
       <c r="O2">
-        <v>0.9872351088201604</v>
+        <v>0.9497712765957448</v>
       </c>
       <c r="P2">
-        <v>689.485</v>
+        <v>892.7850000000001</v>
       </c>
       <c r="Q2">
-        <v>0.1047212940461725</v>
+        <v>0.09721937886575485</v>
       </c>
       <c r="R2">
-        <v>0.9872351088201604</v>
+        <v>0.9497712765957448</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1074.9</v>
+        <v>1659.7</v>
       </c>
       <c r="V2">
-        <v>0.1632594167679222</v>
+        <v>0.1807322066382089</v>
       </c>
       <c r="W2">
-        <v>0.1320476460578559</v>
+        <v>0.1559114634783662</v>
       </c>
       <c r="X2">
-        <v>0.08271184774683492</v>
+        <v>0.07827099259241642</v>
       </c>
       <c r="Y2">
-        <v>0.04933579831102101</v>
+        <v>0.07764047088594973</v>
       </c>
       <c r="Z2">
-        <v>0.1174374437091279</v>
+        <v>0.1432435668951332</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06557648678154986</v>
+        <v>0.06610414289936398</v>
       </c>
       <c r="AC2">
-        <v>-0.06557648678154986</v>
+        <v>-0.06610414289936398</v>
       </c>
       <c r="AD2">
-        <v>6721.5</v>
+        <v>7969.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6721.5</v>
+        <v>7969.2</v>
       </c>
       <c r="AG2">
-        <v>5646.6</v>
+        <v>6309.5</v>
       </c>
       <c r="AH2">
-        <v>0.5051670361880425</v>
+        <v>0.4646113663394044</v>
       </c>
       <c r="AI2">
-        <v>0.548568490467485</v>
+        <v>0.5345550405484267</v>
       </c>
       <c r="AJ2">
-        <v>0.4616780861118833</v>
+        <v>0.4072563207187901</v>
       </c>
       <c r="AK2">
-        <v>0.5051574982778518</v>
+        <v>0.4762461882189548</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>0.1320476460578559</v>
       </c>
       <c r="X3">
-        <v>0.08271184774683492</v>
+        <v>0.08269460955002532</v>
       </c>
       <c r="Y3">
-        <v>0.04933579831102101</v>
+        <v>0.04935303650783061</v>
       </c>
       <c r="Z3">
         <v>0.1174374437091279</v>
@@ -785,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06557648678154986</v>
+        <v>0.06556795675353179</v>
       </c>
       <c r="AC3">
-        <v>-0.06557648678154986</v>
+        <v>-0.06556795675353179</v>
       </c>
       <c r="AD3">
         <v>6721.5</v>
@@ -818,6 +818,128 @@
         <v>0</v>
       </c>
       <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MONETA Money Bank, a.s. (SEP:MONET)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0407</v>
+      </c>
+      <c r="E4">
+        <v>0.0694</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>241.6</v>
+      </c>
+      <c r="L4">
+        <v>0.4524344569288389</v>
+      </c>
+      <c r="M4">
+        <v>203.3</v>
+      </c>
+      <c r="N4">
+        <v>0.07821637426900586</v>
+      </c>
+      <c r="O4">
+        <v>0.8414735099337749</v>
+      </c>
+      <c r="P4">
+        <v>203.3</v>
+      </c>
+      <c r="Q4">
+        <v>0.07821637426900586</v>
+      </c>
+      <c r="R4">
+        <v>0.8414735099337749</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>584.8</v>
+      </c>
+      <c r="V4">
+        <v>0.2249923053247153</v>
+      </c>
+      <c r="W4">
+        <v>0.1797752808988764</v>
+      </c>
+      <c r="X4">
+        <v>0.07384737563480752</v>
+      </c>
+      <c r="Y4">
+        <v>0.1059279052640689</v>
+      </c>
+      <c r="Z4">
+        <v>0.3740543569627347</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06664032904519618</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06664032904519618</v>
+      </c>
+      <c r="AD4">
+        <v>1247.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>1247.7</v>
+      </c>
+      <c r="AG4">
+        <v>662.9000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.3243390782188256</v>
+      </c>
+      <c r="AI4">
+        <v>0.4698904078635182</v>
+      </c>
+      <c r="AJ4">
+        <v>0.2032126544250636</v>
+      </c>
+      <c r="AK4">
+        <v>0.3201642115431056</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>
